--- a/RPC-Matriz-de-precios.xlsx
+++ b/RPC-Matriz-de-precios.xlsx
@@ -759,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2148,8 +2148,120 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="B40" s="17" t="inlineStr">
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Pantalones</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>Pantalón Cargo Gabardina</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Stock express</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>16990</v>
+      </c>
+      <c r="G39" s="13" t="n"/>
+      <c r="H39" s="13" t="n"/>
+      <c r="I39" s="12" t="n">
+        <v>13990</v>
+      </c>
+      <c r="J39" s="13" t="n"/>
+      <c r="K39" s="13" t="n"/>
+      <c r="L39" s="13" t="n"/>
+      <c r="M39" s="14" t="n"/>
+      <c r="N39" s="15" t="inlineStr">
+        <is>
+          <t>Cintura 38-58 · hombre y mujer · opción sin logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="16" t="inlineStr"/>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Pantalón Recto Tipo Docker</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Stock express</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>16990</v>
+      </c>
+      <c r="G40" s="13" t="n"/>
+      <c r="H40" s="13" t="n"/>
+      <c r="I40" s="12" t="n">
+        <v>13990</v>
+      </c>
+      <c r="J40" s="13" t="n"/>
+      <c r="K40" s="13" t="n"/>
+      <c r="L40" s="13" t="n"/>
+      <c r="M40" s="14" t="n"/>
+      <c r="N40" s="15" t="inlineStr">
+        <is>
+          <t>Cintura 38-58 · hombre y mujer · opción sin logo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="16" t="inlineStr"/>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>Pantalón Cargo Poplin</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Stock express</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>13900</v>
+      </c>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="13" t="n"/>
+      <c r="I41" s="12" t="n">
+        <v>8990</v>
+      </c>
+      <c r="J41" s="13" t="n"/>
+      <c r="K41" s="13" t="n"/>
+      <c r="L41" s="13" t="n"/>
+      <c r="M41" s="14" t="n"/>
+      <c r="N41" s="15" t="inlineStr">
+        <is>
+          <t>Tallas S-2XL · modelo unisex</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="B43" s="17" t="inlineStr">
         <is>
           <t>Celdas celestes = tope y piso del rango que ustedes entregaron en el formulario; sólo confirmar/ajustar. Celdas amarillas = precios intermedios y a granel a completar. Si un tramo no aplica, déjalo en blanco.</t>
         </is>
@@ -2157,10 +2269,10 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B40:N40"/>
+    <mergeCell ref="B43:N43"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="M4:M38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Elige Neto o Con IVA" promptTitle="IVA" prompt="Indica si el precio está en neto o con IVA" type="list">
+    <dataValidation sqref="M4:M41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Elige Neto o Con IVA" promptTitle="IVA" prompt="Indica si el precio está en neto o con IVA" type="list">
       <formula1>"Neto (+IVA),Con IVA incluido"</formula1>
     </dataValidation>
   </dataValidations>
